--- a/backtest_runs/20260410_193731/by_symbol/TOWL/TOWL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TOWL/TOWL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-4753.340000000001</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>95518.53</v>
@@ -633,7 +633,7 @@
         <v>-3323.829999999993</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>92194.70000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>92194.70000000001</v>
@@ -863,7 +863,7 @@
         <v>-254.3300000000055</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>93475.12</v>
@@ -955,7 +955,7 @@
         <v>-666.519999999992</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>92808.60000000001</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>92808.60000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-2622.229999999995</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>90624.87000000001</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>90624.87000000001</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>90624.87000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-2937.949999999995</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>91063.37000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-1157.640000000006</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>89905.73000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-631.439999999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>89274.29000000001</v>
